--- a/cache/open_items_2026-07-13.xlsx
+++ b/cache/open_items_2026-07-13.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N328"/>
+  <dimension ref="A1:N331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -11320,13 +11320,13 @@
         </is>
       </c>
     </row>
-    <row r="197" ht="90" customHeight="1">
+    <row r="197" ht="45" customHeight="1">
       <c r="A197" s="2" t="n">
         <v>196</v>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>REGIME-INTRADAY-BAR-ANCHOR</t>
         </is>
       </c>
       <c r="C197" s="9" t="inlineStr">
@@ -11336,22 +11336,22 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Regime / Data Integrity</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>Regime inputs read partial intraday bar</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>VIX + QQQ-SPY spread used EODHD's still-forming intraday bar instead of last completed session</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+          <t>drop_partial_today_bar() helper; regime_accuracy --synthetic-labels validates risk_off/panic</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
@@ -11364,23 +11364,23 @@
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
+          <t>9899c16f4</t>
         </is>
       </c>
       <c r="N197" s="8" t="inlineStr"/>
     </row>
-    <row r="198" ht="45" customHeight="1">
+    <row r="198" ht="90" customHeight="1">
       <c r="A198" s="2" t="n">
         <v>197</v>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>RISK-CB-PAPER-OFF</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C198" s="9" t="inlineStr">
@@ -11390,22 +11390,22 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>Risk / Paper</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Circuit breaker fully disabled for paper trading</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>drawdown circuit breaker OFF (config disabled flag honored in portfolio_tracker), 90-day Slack review reminder via daily scan</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>config.json circuit_breaker + portfolio_tracker + swing_trade reminder</t>
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr"/>
@@ -11418,23 +11418,23 @@
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>d85c5ac2d</t>
+          <t>4442fa300</t>
         </is>
       </c>
       <c r="N198" s="8" t="inlineStr"/>
     </row>
-    <row r="199" ht="105" customHeight="1">
+    <row r="199" ht="45" customHeight="1">
       <c r="A199" s="2" t="n">
         <v>198</v>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>RISK-CB-PAPER-OFF</t>
         </is>
       </c>
       <c r="C199" s="9" t="inlineStr">
@@ -11444,31 +11444,27 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Risk / Paper</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Circuit breaker fully disabled for paper trading</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>drawdown circuit breaker OFF (config disabled flag honored in portfolio_tracker), 90-day Slack review reminder via daily scan</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
+          <t>config.json circuit_breaker + portfolio_tracker + swing_trade reminder</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr"/>
       <c r="I199" s="5" t="inlineStr"/>
-      <c r="J199" s="5" t="inlineStr">
-        <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
-        </is>
-      </c>
+      <c r="J199" s="5" t="inlineStr"/>
       <c r="K199" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11476,27 +11472,23 @@
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
-        </is>
-      </c>
-      <c r="N199" s="8" t="inlineStr">
-        <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="90" customHeight="1">
+          <t>d85c5ac2d</t>
+        </is>
+      </c>
+      <c r="N199" s="8" t="inlineStr"/>
+    </row>
+    <row r="200" ht="105" customHeight="1">
       <c r="A200" s="2" t="n">
         <v>199</v>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>NEWS-DESAT-1</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C200" s="9" t="inlineStr">
@@ -11506,27 +11498,31 @@
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>Scoring</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>News sentiment saturation</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>compute_news_sentiment_score scored each insight by discrete +/-1 label and omitted neutral from denominator -&gt; 86% of universe pinned bullish, 73% pegged source_score=1.0, only 1 bearish in 908; NEWS_MOMENTUM tag fired on 86%; catalyst pillar awarded ~+1.71 pts to nearly every name (non-discriminating constant).</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>continuous_polarity flag (scoring.news_sentiment, default ON): average continuous (pos-neg) polarity from sentiment_reasoning over ALL insights, neutral=0 in denominator. Recalibrated NEWS_MOMENTUM tag + catalyst-pts thresholds to new compressed scale. Result: bullish 86-&gt;15%, pegged 73-&gt;0%, tag 86-&gt;15%. Rollback=false reproduces legacy exactly.</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr"/>
       <c r="I200" s="5" t="inlineStr"/>
-      <c r="J200" s="5" t="inlineStr"/>
+      <c r="J200" s="5" t="inlineStr">
+        <is>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+        </is>
+      </c>
       <c r="K200" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11534,23 +11530,27 @@
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
-        </is>
-      </c>
-      <c r="N200" s="8" t="inlineStr"/>
-    </row>
-    <row r="201" ht="60" customHeight="1">
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N200" s="8" t="inlineStr">
+        <is>
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="90" customHeight="1">
       <c r="A201" s="2" t="n">
         <v>200</v>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>SIGNAL-GATEFLOOR-70</t>
+          <t>NEWS-DESAT-1</t>
         </is>
       </c>
       <c r="C201" s="9" t="inlineStr">
@@ -11560,22 +11560,22 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>Signal Scanner</t>
+          <t>Scoring</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>Raise composite quality gate_floor 60-&gt;70</t>
+          <t>News sentiment saturation</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>Dual-log audit: composite 60-69 band loses (picks PF 0.79/signal 0.55 full; 65-69 PF 0.20/0.44 post-ranker); 70-89 is the edge (1.35/1.70). Ranker not salvaging 65-69.</t>
+          <t>compute_news_sentiment_score scored each insight by discrete +/-1 label and omitted neutral from denominator -&gt; 86% of universe pinned bullish, 73% pegged source_score=1.0, only 1 bearish in 908; NEWS_MOMENTUM tag fired on 86%; catalyst pillar awarded ~+1.71 pts to nearly every name (non-discriminating constant).</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>config.regime_conditional_ranker.gate_floor 60-&gt;70 + _gate_floor_audit note; backup config.json.bak.20260706_113721; WF wf_accuracy_20260706 corroborating OOS</t>
+          <t>continuous_polarity flag (scoring.news_sentiment, default ON): average continuous (pos-neg) polarity from sentiment_reasoning over ALL insights, neutral=0 in denominator. Recalibrated NEWS_MOMENTUM tag + catalyst-pts thresholds to new compressed scale. Result: bullish 86-&gt;15%, pegged 73-&gt;0%, tag 86-&gt;15%. Rollback=false reproduces legacy exactly.</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr"/>
@@ -11588,23 +11588,23 @@
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>962b0baa2</t>
+          <t>1d6fdb14a</t>
         </is>
       </c>
       <c r="N201" s="8" t="inlineStr"/>
     </row>
-    <row r="202" ht="75" customHeight="1">
+    <row r="202" ht="60" customHeight="1">
       <c r="A202" s="2" t="n">
         <v>201</v>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>CHOPPY-BREAKOUT-DEMOTE</t>
+          <t>SIGNAL-GATEFLOOR-70</t>
         </is>
       </c>
       <c r="C202" s="9" t="inlineStr">
@@ -11614,22 +11614,22 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>Signal quality</t>
+          <t>Signal Scanner</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>Demote Breakout-Expansion BUYs to WATCH in non-trending regimes</t>
+          <t>Raise composite quality gate_floor 60-&gt;70</t>
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>Actual BUY verdicts lost in choppy (hit 40%, -1.74%); breakout BUYs = 46% of book at PF 0.49. Triangulated across picks_history robustness battery + 06-11 BUY&lt;WATCH audit + 06-08 history audit + owner CSV D5 join.</t>
+          <t>Dual-log audit: composite 60-69 band loses (picks PF 0.79/signal 0.55 full; 65-69 PF 0.20/0.44 post-ranker); 70-89 is the edge (1.35/1.70). Ranker not salvaging 65-69.</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>Flag-gated config.choppy_breakout_demote (regime-locked, demote-to-WATCH, reversible) + gate in decision_engine._compute_final_verdict_impl _promote block; reprocess_bundle now passes config. Validated: removes losing half, book PF 0.91-&gt;1.51; 4-case behavioral test passes.</t>
+          <t>config.regime_conditional_ranker.gate_floor 60-&gt;70 + _gate_floor_audit note; backup config.json.bak.20260706_113721; WF wf_accuracy_20260706 corroborating OOS</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr"/>
@@ -11642,23 +11642,23 @@
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>48f6a2fbf</t>
+          <t>962b0baa2</t>
         </is>
       </c>
       <c r="N202" s="8" t="inlineStr"/>
     </row>
-    <row r="203" ht="90" customHeight="1">
+    <row r="203" ht="75" customHeight="1">
       <c r="A203" s="2" t="n">
         <v>202</v>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>BREAKOUT-BYPASS-LIVE</t>
+          <t>CHOPPY-BREAKOUT-DEMOTE</t>
         </is>
       </c>
       <c r="C203" s="9" t="inlineStr">
@@ -11668,22 +11668,22 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Signals · Gating</t>
+          <t>Signal quality</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>Breakout-alpha entry_quality bypass enabled</t>
+          <t>Demote Breakout-Expansion BUYs to WATCH in non-trending regimes</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>Alpha setups (VCP/52wk/10WP) were demoted to WATCH by entry_quality EXTENDED/MISSED gate (their natural state) + hidden under broad families. Surfaced granular setup_type in scanner + enabled entry_quality_breakout_bypass for alpha sub-types only (TC/BE excluded). Regime score floor still applies. Paper observation; backtest cant validate verdict changes.</t>
+          <t>Actual BUY verdicts lost in choppy (hit 40%, -1.74%); breakout BUYs = 46% of book at PF 0.49. Triangulated across picks_history robustness battery + 06-11 BUY&lt;WATCH audit + 06-08 history audit + owner CSV D5 join.</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>config.entry_quality_breakout_bypass._enabled=true + analysis.make_decision bypass + server setup_type surfacing</t>
+          <t>Flag-gated config.choppy_breakout_demote (regime-locked, demote-to-WATCH, reversible) + gate in decision_engine._compute_final_verdict_impl _promote block; reprocess_bundle now passes config. Validated: removes losing half, book PF 0.91-&gt;1.51; 4-case behavioral test passes.</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr"/>
@@ -11696,12 +11696,12 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>cc4338d9d</t>
+          <t>48f6a2fbf</t>
         </is>
       </c>
       <c r="N203" s="8" t="inlineStr"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-VERDICT-ALIGN</t>
+          <t>SCHWAB-REALBUY-DESKS</t>
         </is>
       </c>
       <c r="C204" s="9" t="inlineStr">
@@ -11722,22 +11722,22 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>Signals · Sizing</t>
+          <t>Signals / Desks</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>Verdict=BUY masked 0-conviction names in scanner + executor</t>
+          <t>Live 'real buy' validator on desk cards</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>10 of 12 BUY-verdict names in risk_on_choppy were conviction=AVOID/size_mult 0; scanner ranked + executor traded them as if real buys, killing user confidence + buying 0-conviction names (ARMK/PBI/WDC)</t>
+          <t>Re-decide every desk BUY off live Schwab data (EMA stack, RSI/ADX, RVOL, halt) + scan bias/bear-score + desk edge tier; stamp REAL BUY/MARGINAL/UNVERIFIED/NOT REAL</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>executor.py conviction gate (skip 0-size, scale by size_mult); surface-signal.jsx conviction-aware Top Buys sort + tier column in Essentials</t>
+          <t>real_buy_gate.py shared gate; screener_desks _tag stamps _realbuy; surface-desks.jsx badge; auto-refresh on 5-min overlay</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr"/>
@@ -11750,23 +11750,23 @@
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>6a5a50549</t>
+          <t>9899c16f4</t>
         </is>
       </c>
       <c r="N204" s="8" t="inlineStr"/>
     </row>
-    <row r="205" ht="45" customHeight="1">
+    <row r="205" ht="90" customHeight="1">
       <c r="A205" s="2" t="n">
         <v>204</v>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>BREAKOUT-BYPASS-LIVE</t>
         </is>
       </c>
       <c r="C205" s="9" t="inlineStr">
@@ -11776,39 +11776,27 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Signals · Gating</t>
         </is>
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>Breakout-alpha entry_quality bypass enabled</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>Alpha setups (VCP/52wk/10WP) were demoted to WATCH by entry_quality EXTENDED/MISSED gate (their natural state) + hidden under broad families. Surfaced granular setup_type in scanner + enabled entry_quality_breakout_bypass for alpha sub-types only (TC/BE excluded). Regime score floor still applies. Paper observation; backtest cant validate verdict changes.</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
-        </is>
-      </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I205" s="5" t="inlineStr">
-        <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
-        </is>
-      </c>
-      <c r="J205" s="5" t="inlineStr">
-        <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
-        </is>
-      </c>
+          <t>config.entry_quality_breakout_bypass._enabled=true + analysis.make_decision bypass + server setup_type surfacing</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr"/>
+      <c r="I205" s="5" t="inlineStr"/>
+      <c r="J205" s="5" t="inlineStr"/>
       <c r="K205" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11816,27 +11804,23 @@
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
-        </is>
-      </c>
-      <c r="N205" s="8" t="inlineStr">
-        <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="90" customHeight="1">
+          <t>cc4338d9d</t>
+        </is>
+      </c>
+      <c r="N205" s="8" t="inlineStr"/>
+    </row>
+    <row r="206" ht="60" customHeight="1">
       <c r="A206" s="2" t="n">
         <v>205</v>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>CONVICTION-VERDICT-ALIGN</t>
         </is>
       </c>
       <c r="C206" s="9" t="inlineStr">
@@ -11846,39 +11830,27 @@
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Signals · Sizing</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Verdict=BUY masked 0-conviction names in scanner + executor</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>10 of 12 BUY-verdict names in risk_on_choppy were conviction=AVOID/size_mult 0; scanner ranked + executor traded them as if real buys, killing user confidence + buying 0-conviction names (ARMK/PBI/WDC)</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
-        </is>
-      </c>
-      <c r="H206" s="2" t="inlineStr">
-        <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I206" s="5" t="inlineStr">
-        <is>
-          <t>Low / High (transparency + future-proof)</t>
-        </is>
-      </c>
-      <c r="J206" s="5" t="inlineStr">
-        <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
-        </is>
-      </c>
+          <t>executor.py conviction gate (skip 0-size, scale by size_mult); surface-signal.jsx conviction-aware Top Buys sort + tier column in Essentials</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr"/>
+      <c r="I206" s="5" t="inlineStr"/>
+      <c r="J206" s="5" t="inlineStr"/>
       <c r="K206" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11886,27 +11858,23 @@
       </c>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N206" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="75" customHeight="1">
+          <t>6a5a50549</t>
+        </is>
+      </c>
+      <c r="N206" s="8" t="inlineStr"/>
+    </row>
+    <row r="207" ht="45" customHeight="1">
       <c r="A207" s="2" t="n">
         <v>206</v>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M21-INFRA</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C207" s="9" t="inlineStr">
@@ -11916,27 +11884,39 @@
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
-        </is>
-      </c>
-      <c r="H207" s="2" t="inlineStr"/>
-      <c r="I207" s="5" t="inlineStr"/>
-      <c r="J207" s="5" t="inlineStr"/>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
+        </is>
+      </c>
+      <c r="J207" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+        </is>
+      </c>
       <c r="K207" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11944,15 +11924,19 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N207" s="8" t="inlineStr"/>
+          <t>363984181</t>
+        </is>
+      </c>
+      <c r="N207" s="8" t="inlineStr">
+        <is>
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="90" customHeight="1">
       <c r="A208" s="2" t="n">
@@ -11960,7 +11944,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M22-DATA</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C208" s="9" t="inlineStr">
@@ -11970,27 +11954,39 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
-        </is>
-      </c>
-      <c r="H208" s="2" t="inlineStr"/>
-      <c r="I208" s="5" t="inlineStr"/>
-      <c r="J208" s="5" t="inlineStr"/>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="inlineStr">
+        <is>
+          <t>Low / High (transparency + future-proof)</t>
+        </is>
+      </c>
+      <c r="J208" s="5" t="inlineStr">
+        <is>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+        </is>
+      </c>
       <c r="K208" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11998,7 +11994,7 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
@@ -12006,15 +12002,19 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="N208" s="8" t="inlineStr"/>
-    </row>
-    <row r="209" ht="90" customHeight="1">
+      <c r="N208" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="75" customHeight="1">
       <c r="A209" s="2" t="n">
         <v>208</v>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M23-MODES</t>
+          <t>STRUCT-TARGETS-M21-INFRA</t>
         </is>
       </c>
       <c r="C209" s="9" t="inlineStr">
@@ -12029,17 +12029,17 @@
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
+          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
+          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
+          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr"/>
@@ -12062,13 +12062,13 @@
       </c>
       <c r="N209" s="8" t="inlineStr"/>
     </row>
-    <row r="210" ht="75" customHeight="1">
+    <row r="210" ht="90" customHeight="1">
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M24-VALIDATION</t>
+          <t>STRUCT-TARGETS-M22-DATA</t>
         </is>
       </c>
       <c r="C210" s="9" t="inlineStr">
@@ -12083,17 +12083,17 @@
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.4 — regression suite + monitoring</t>
+          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
+          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
+          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
@@ -12116,13 +12116,13 @@
       </c>
       <c r="N210" s="8" t="inlineStr"/>
     </row>
-    <row r="211" ht="75" customHeight="1">
+    <row r="211" ht="90" customHeight="1">
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>STRUCT-TARGETS-M23-MODES</t>
         </is>
       </c>
       <c r="C211" s="9" t="inlineStr">
@@ -12132,22 +12132,22 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr"/>
@@ -12160,23 +12160,23 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N211" s="8" t="inlineStr"/>
     </row>
-    <row r="212" ht="60" customHeight="1">
+    <row r="212" ht="75" customHeight="1">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>STRUCT-TARGETS-M24-VALIDATION</t>
         </is>
       </c>
       <c r="C212" s="9" t="inlineStr">
@@ -12186,39 +12186,27 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Structural targets · M2.4 — regression suite + monitoring</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
-        </is>
-      </c>
-      <c r="H212" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I212" s="5" t="inlineStr">
-        <is>
-          <t>Win: continuous drift visibility between alert events.</t>
-        </is>
-      </c>
-      <c r="J212" s="5" t="inlineStr">
-        <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
-        </is>
-      </c>
+          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="5" t="inlineStr"/>
+      <c r="J212" s="5" t="inlineStr"/>
       <c r="K212" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12226,27 +12214,23 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
-        </is>
-      </c>
-      <c r="N212" s="8" t="inlineStr">
-        <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="45" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N212" s="8" t="inlineStr"/>
+    </row>
+    <row r="213" ht="75" customHeight="1">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C213" s="9" t="inlineStr">
@@ -12256,39 +12240,27 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
-        </is>
-      </c>
-      <c r="H213" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I213" s="5" t="inlineStr">
-        <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
-        </is>
-      </c>
-      <c r="J213" s="5" t="inlineStr">
-        <is>
-          <t>Trivial.</t>
-        </is>
-      </c>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="5" t="inlineStr"/>
+      <c r="J213" s="5" t="inlineStr"/>
       <c r="K213" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12296,27 +12268,23 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
-        </is>
-      </c>
-      <c r="N213" s="8" t="inlineStr">
-        <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="105" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N213" s="8" t="inlineStr"/>
+    </row>
+    <row r="214" ht="60" customHeight="1">
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C214" s="9" t="inlineStr">
@@ -12326,29 +12294,37 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
-        </is>
-      </c>
-      <c r="H214" s="2" t="inlineStr"/>
-      <c r="I214" s="5" t="inlineStr"/>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I214" s="5" t="inlineStr">
+        <is>
+          <t>Win: continuous drift visibility between alert events.</t>
+        </is>
+      </c>
       <c r="J214" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K214" s="12" t="inlineStr">
@@ -12358,27 +12334,27 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N214" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="105" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="45" customHeight="1">
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C215" s="9" t="inlineStr">
@@ -12393,24 +12369,32 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
-        </is>
-      </c>
-      <c r="H215" s="2" t="inlineStr"/>
-      <c r="I215" s="5" t="inlineStr"/>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I215" s="5" t="inlineStr">
+        <is>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
       <c r="J215" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K215" s="12" t="inlineStr">
@@ -12420,27 +12404,27 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N215" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="45" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="105" customHeight="1">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C216" s="9" t="inlineStr">
@@ -12450,37 +12434,29 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
-        </is>
-      </c>
-      <c r="H216" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I216" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="5" t="inlineStr"/>
       <c r="J216" s="5" t="inlineStr">
         <is>
-          <t>All reads use ?? fallbacks.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K216" s="12" t="inlineStr">
@@ -12495,22 +12471,22 @@
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N216" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="45" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="105" customHeight="1">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C217" s="9" t="inlineStr">
@@ -12520,35 +12496,31 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
-        </is>
-      </c>
-      <c r="H217" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I217" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J217" s="5" t="inlineStr"/>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="5" t="inlineStr"/>
+      <c r="J217" s="5" t="inlineStr">
+        <is>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+        </is>
+      </c>
       <c r="K217" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12561,22 +12533,22 @@
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N217" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="105" customHeight="1">
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="45" customHeight="1">
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C218" s="9" t="inlineStr">
@@ -12586,37 +12558,37 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>1.5 hrs</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>Low (no behavior change)</t>
+          <t>Low risk / Medium win (consistency)</t>
         </is>
       </c>
       <c r="J218" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+          <t>All reads use ?? fallbacks.</t>
         </is>
       </c>
       <c r="K218" s="12" t="inlineStr">
@@ -12631,12 +12603,12 @@
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N218" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
         </is>
       </c>
     </row>
@@ -12646,7 +12618,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>UNIVERSE-NASDAQ-1000</t>
+          <t>RULE-1</t>
         </is>
       </c>
       <c r="C219" s="9" t="inlineStr">
@@ -12656,26 +12628,34 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Universe</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>NASDAQ 1000 liquidity gate</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>get_nasdaq_all replaced full 4805-name exchange list with top-1000 by dollar volume (one bulk_eod call); config nasdaq_all_top_n/min_dollar_vol</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_nasdaq_all + config.json + swing_trade.py</t>
-        </is>
-      </c>
-      <c r="H219" s="2" t="inlineStr"/>
-      <c r="I219" s="5" t="inlineStr"/>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I219" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
       <c r="J219" s="5" t="inlineStr"/>
       <c r="K219" s="12" t="inlineStr">
         <is>
@@ -12684,23 +12664,27 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>ab1deacef</t>
-        </is>
-      </c>
-      <c r="N219" s="8" t="inlineStr"/>
-    </row>
-    <row r="220" ht="45" customHeight="1">
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N219" s="8" t="inlineStr">
+        <is>
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="105" customHeight="1">
       <c r="A220" s="2" t="n">
         <v>219</v>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-KAIROS-DOSSIER</t>
+          <t>TARGET-SOURCES-P1</t>
         </is>
       </c>
       <c r="C220" s="9" t="inlineStr">
@@ -12710,27 +12694,39 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Kairos</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Ask Kairos cross-lens ticker dossier (§4)</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>composite verdict + 9 lens stances + ML projection injected as LLM context; fallbackAnswer offline</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html kaiTickerDossier</t>
-        </is>
-      </c>
-      <c r="H220" s="2" t="inlineStr"/>
-      <c r="I220" s="5" t="inlineStr"/>
-      <c r="J220" s="5" t="inlineStr"/>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>1.5 hrs</t>
+        </is>
+      </c>
+      <c r="I220" s="5" t="inlineStr">
+        <is>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J220" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K220" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12738,15 +12734,19 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>e3baa715f</t>
-        </is>
-      </c>
-      <c r="N220" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N220" s="8" t="inlineStr">
+        <is>
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="45" customHeight="1">
       <c r="A221" s="2" t="n">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>REGIME-ACCURACY-TEST</t>
+          <t>UNIVERSE-NASDAQ-1000</t>
         </is>
       </c>
       <c r="C221" s="9" t="inlineStr">
@@ -12764,22 +12764,22 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Validation / Regime</t>
+          <t>Universe</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Regime-classification accuracy test (principle 18)</t>
+          <t>NASDAQ 1000 liquidity gate</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
+          <t>get_nasdaq_all replaced full 4805-name exchange list with top-1000 by dollar volume (one bulk_eod call); config nasdaq_all_top_n/min_dollar_vol</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>scripts/regime_accuracy.py</t>
+          <t>data_fetcher.get_nasdaq_all + config.json + swing_trade.py</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
@@ -12792,48 +12792,48 @@
       </c>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
+          <t>ab1deacef</t>
         </is>
       </c>
       <c r="N221" s="8" t="inlineStr"/>
     </row>
-    <row r="222" ht="90" customHeight="1">
+    <row r="222" ht="45" customHeight="1">
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>MORNING-BRIEF-STALE</t>
-        </is>
-      </c>
-      <c r="C222" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>STOCKSMITH-KAIROS-DOSSIER</t>
+        </is>
+      </c>
+      <c r="C222" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Alerts</t>
+          <t>V2 Dashboard / Kairos</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Morning briefing exit=2 (stale tickers.json)</t>
+          <t>Ask Kairos cross-lens ticker dossier (§4)</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>morning_briefing.py aborts (exit 2) when infra/prototype/tickers.json &gt;24h old. Root cause: build_data.py (writes tickers.json at scan end) intermittently exceeds the 180s subprocess timeout in swing_trade.py on cold caches -&gt; tickers.json not refreshed -&gt; stale -&gt; briefing aborts. Compounded by transient Slack DNS failures when the Mac is asleep at 6:30am</t>
+          <t>composite verdict + 9 lens stances + ML projection injected as LLM context; fallbackAnswer offline</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>Raised build_data.py subprocess timeout 180-&gt;360s in swing_trade.py (2x headroom). Manually refreshed tickers.json. Residual: machine must be awake/online at 6:30 PT for briefing+all alerts to post</t>
+          <t>Stocksmith.html kaiTickerDossier</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr"/>
@@ -12846,48 +12846,48 @@
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>e7721f05c</t>
+          <t>e3baa715f</t>
         </is>
       </c>
       <c r="N222" s="8" t="inlineStr"/>
     </row>
-    <row r="223" ht="90" customHeight="1">
+    <row r="223" ht="45" customHeight="1">
       <c r="A223" s="2" t="n">
         <v>222</v>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>SIGNAL-ALERTS-1</t>
-        </is>
-      </c>
-      <c r="C223" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>REGIME-ACCURACY-TEST</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Alerts</t>
+          <t>Validation / Regime</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Daily WATCH-to-BUY flip + new Elite Pick alerts</t>
+          <t>Regime-classification accuracy test (principle 18)</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>Owner wanted Slack alerts for (a) firm BUY-candidate from entry-watcher, (b) names flipping to BUY day-over-day, (c) new Elite Picks per mode</t>
+          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>entry_watch.py: distinct shadow BUY-CANDIDATE message (#a). signal_alerts.py: day-over-day diff of per-mode BUY lists (buy_candidates/medium_term_picks/long_term_picks) + elite_picks vs data/signal_alert_snapshot.json; grouped digest; LIVE to owner Slack with composite-score caveat; launchd com.swingtrade.signal-alerts 7:15 PT daily. Zero EODHD</t>
+          <t>scripts/regime_accuracy.py</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr"/>
@@ -12900,23 +12900,23 @@
       </c>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>116e27f63</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N223" s="8" t="inlineStr"/>
     </row>
-    <row r="224" ht="75" customHeight="1">
+    <row r="224" ht="90" customHeight="1">
       <c r="A224" s="2" t="n">
         <v>223</v>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>SLEEVE-ALERTS</t>
+          <t>MORNING-BRIEF-STALE</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -12931,17 +12931,17 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Dedicated catalyst-sleeve signal alerts</t>
+          <t>Morning briefing exit=2 (stale tickers.json)</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Entry-watcher covers price-action setups (pullback/breakout/impulse) but the 7 catalyst sleeves (PEAD/Insider/ESP/MeanRev/Momentum/DefRot) had no dedicated alert — they only reached Slack indirectly via flip/elite digests. Per principle 14 these are the higher-mechanism signals (PEAD PF 2.04, Momentum 1.53)</t>
+          <t>morning_briefing.py aborts (exit 2) when infra/prototype/tickers.json &gt;24h old. Root cause: build_data.py (writes tickers.json at scan end) intermittently exceeds the 180s subprocess timeout in swing_trade.py on cold caches -&gt; tickers.json not refreshed -&gt; stale -&gt; briefing aborts. Compounded by transient Slack DNS failures when the Mac is asleep at 6:30am</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>signal_alerts.py: added SLEEVES dimension; _current_state tracks &lt;field&gt;.fired per sleeve; daily diff emits '🧬 New catalyst signal(s)' clean card on new entrants; Phase-1 paper-validation note. Fire rarely (0 today) so low-noise/high-value. Snapshot re-seeded with sleeves key</t>
+          <t>Raised build_data.py subprocess timeout 180-&gt;360s in swing_trade.py (2x headroom). Manually refreshed tickers.json. Residual: machine must be awake/online at 6:30 PT for briefing+all alerts to post</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr"/>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>fa8835903</t>
+          <t>e7721f05c</t>
         </is>
       </c>
       <c r="N224" s="8" t="inlineStr"/>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>WEEKEND-PHANTOMS</t>
+          <t>SIGNAL-ALERTS-1</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -12980,22 +12980,22 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Data Quality</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
+          <t>Daily WATCH-to-BUY flip + new Elite Pick alerts</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
+          <t>Owner wanted Slack alerts for (a) firm BUY-candidate from entry-watcher, (b) names flipping to BUY day-over-day, (c) new Elite Picks per mode</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
+          <t>entry_watch.py: distinct shadow BUY-CANDIDATE message (#a). signal_alerts.py: day-over-day diff of per-mode BUY lists (buy_candidates/medium_term_picks/long_term_picks) + elite_picks vs data/signal_alert_snapshot.json; grouped digest; LIVE to owner Slack with composite-score caveat; launchd com.swingtrade.signal-alerts 7:15 PT daily. Zero EODHD</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr"/>
@@ -13008,12 +13008,12 @@
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>116e27f63</t>
         </is>
       </c>
       <c r="N225" s="8" t="inlineStr"/>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>BT-GUARD-1</t>
+          <t>SLEEVE-ALERTS</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -13034,22 +13034,22 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Backtest Infrastructure</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Backtest min_score guard rail</t>
+          <t>Dedicated catalyst-sleeve signal alerts</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
+          <t>Entry-watcher covers price-action setups (pullback/breakout/impulse) but the 7 catalyst sleeves (PEAD/Insider/ESP/MeanRev/Momentum/DefRot) had no dedicated alert — they only reached Slack indirectly via flip/elite digests. Per principle 14 these are the higher-mechanism signals (PEAD PF 2.04, Momentum 1.53)</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
+          <t>signal_alerts.py: added SLEEVES dimension; _current_state tracks &lt;field&gt;.fired per sleeve; daily diff emits '🧬 New catalyst signal(s)' clean card on new entrants; Phase-1 paper-validation note. Fire rarely (0 today) so low-noise/high-value. Snapshot re-seeded with sleeves key</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr"/>
@@ -13062,23 +13062,23 @@
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>d754830</t>
+          <t>fa8835903</t>
         </is>
       </c>
       <c r="N226" s="8" t="inlineStr"/>
     </row>
-    <row r="227" ht="105" customHeight="1">
+    <row r="227" ht="90" customHeight="1">
       <c r="A227" s="2" t="n">
         <v>226</v>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>BULLALGO-1</t>
+          <t>WEEKEND-PHANTOMS</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -13088,22 +13088,22 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>BullVeda</t>
+          <t>Audit Trail / Data Quality</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>BullAlgo — transparent LuxAlgo-style overlays + MCDX + Price Action</t>
+          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>Ownable, inspectable reproduction of LuxAlgo Signals&amp;Overlays + Price Action Concepts + MCDX, replacing the TradingView black box; every layer is a standard auditable indicator</t>
+          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>bullalgo.py engines (Confirmation/Signals-Overlays screener/PAC screener/chart-series/PAC-chart/MCDX); server.py 4 endpoints /api/bullalgo/*; pattern_data SWING_1H mode; isolated test benches bullalgo-test.html + setup-tv-lab.html; PRODUCTION Overview integration in lens-overview.jsx (OverviewMcdx synced strip + interactive/expand setup chart + Setup&lt;-&gt;PriceAction toggle). Display-only, real data, NOT identical to LuxAlgo (transparent approximation)</t>
+          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr"/>
@@ -13116,12 +13116,12 @@
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>296777349</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N227" s="8" t="inlineStr"/>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>BULLALGO-FOOTPRINT</t>
+          <t>BT-GUARD-1</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -13142,22 +13142,22 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>BullVeda Lenses</t>
+          <t>Backtest Infrastructure</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Real institutional footprint strip</t>
+          <t>Backtest min_score guard rail</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>MCDX is interpretive momentum math (no order flow); users asked why we cant show real smart-money detail</t>
+          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>Added /api/bullalgo/{t}/footprint + bullalgo.footprint() aggregating REAL attributable signals: OBV/AD accumulation (live), insider Form 4 net (SEC, value-filtered), 13F institutional holders + QoQ change (EODHD). Rendered as honest counterpart strip under MCDX. No new data license.</t>
+          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr"/>
@@ -13170,23 +13170,23 @@
       </c>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>b3314aaf2</t>
+          <t>d754830</t>
         </is>
       </c>
       <c r="N228" s="8" t="inlineStr"/>
     </row>
-    <row r="229" ht="60" customHeight="1">
+    <row r="229" ht="105" customHeight="1">
       <c r="A229" s="2" t="n">
         <v>228</v>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>BULLALGO-LENS</t>
+          <t>BULLALGO-1</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -13196,22 +13196,22 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>BullVeda Lenses</t>
+          <t>BullVeda</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>BullAlgo native lens + MCDX alignment</t>
+          <t>BullAlgo — transparent LuxAlgo-style overlays + MCDX + Price Action</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>Ported bullalgo-test.html prototype into a native per-ticker lens (16th, in-house LuxAlgo replacement for removed tv lens); MCDX money-flow misaligned with price chart</t>
+          <t>Ownable, inspectable reproduction of LuxAlgo Signals&amp;Overlays + Price Action Concepts + MCDX, replacing the TradingView black box; every layer is a standard auditable indicator</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>lens-bullalgo.jsx + lens-bullalgo.css scoped; registered in LENSES/detail-panel/dev-loader/CapStudio; backend mcdx_series emits whitespace warmup points so bar counts match (180==180) + minimumWidth:64 on both price scales</t>
+          <t>bullalgo.py engines (Confirmation/Signals-Overlays screener/PAC screener/chart-series/PAC-chart/MCDX); server.py 4 endpoints /api/bullalgo/*; pattern_data SWING_1H mode; isolated test benches bullalgo-test.html + setup-tv-lab.html; PRODUCTION Overview integration in lens-overview.jsx (OverviewMcdx synced strip + interactive/expand setup chart + Setup&lt;-&gt;PriceAction toggle). Display-only, real data, NOT identical to LuxAlgo (transparent approximation)</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr"/>
@@ -13229,18 +13229,18 @@
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>b3314aaf2</t>
+          <t>296777349</t>
         </is>
       </c>
       <c r="N229" s="8" t="inlineStr"/>
     </row>
-    <row r="230" ht="60" customHeight="1">
+    <row r="230" ht="75" customHeight="1">
       <c r="A230" s="2" t="n">
         <v>229</v>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>LENS-PLAN-PERMODE-TARGETS</t>
+          <t>BULLALGO-FOOTPRINT</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -13250,22 +13250,22 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Plan</t>
+          <t>BullVeda Lenses</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
+          <t>Real institutional footprint strip</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
+          <t>MCDX is interpretive momentum math (no order flow); users asked why we cant show real smart-money detail</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
+          <t>Added /api/bullalgo/{t}/footprint + bullalgo.footprint() aggregating REAL attributable signals: OBV/AD accumulation (live), insider Form 4 net (SEC, value-filtered), 13F institutional holders + QoQ change (EODHD). Rendered as honest counterpart strip under MCDX. No new data license.</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
@@ -13278,23 +13278,23 @@
       </c>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>99cff7117</t>
+          <t>b3314aaf2</t>
         </is>
       </c>
       <c r="N230" s="8" t="inlineStr"/>
     </row>
-    <row r="231" ht="45" customHeight="1">
+    <row r="231" ht="60" customHeight="1">
       <c r="A231" s="2" t="n">
         <v>230</v>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>SURFACE-WATCHLIST-MOCK</t>
+          <t>BULLALGO-LENS</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -13304,22 +13304,22 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Watchlist</t>
+          <t>BullVeda Lenses</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
+          <t>BullAlgo native lens + MCDX alignment</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
+          <t>Ported bullalgo-test.html prototype into a native per-ticker lens (16th, in-house LuxAlgo replacement for removed tv lens); MCDX money-flow misaligned with price chart</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
+          <t>lens-bullalgo.jsx + lens-bullalgo.css scoped; registered in LENSES/detail-panel/dev-loader/CapStudio; backend mcdx_series emits whitespace warmup points so bar counts match (180==180) + minimumWidth:64 on both price scales</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr"/>
@@ -13332,23 +13332,23 @@
       </c>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>99cff7117</t>
+          <t>b3314aaf2</t>
         </is>
       </c>
       <c r="N231" s="8" t="inlineStr"/>
     </row>
-    <row r="232" ht="45" customHeight="1">
+    <row r="232" ht="60" customHeight="1">
       <c r="A232" s="2" t="n">
         <v>231</v>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
+          <t>LENS-PLAN-PERMODE-TARGETS</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
@@ -13358,22 +13358,22 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>BullVeda · Plan</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -13386,12 +13386,12 @@
       </c>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>99cff7117</t>
         </is>
       </c>
       <c r="N232" s="8" t="inlineStr"/>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
+          <t>SURFACE-WATCHLIST-MOCK</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
@@ -13412,22 +13412,22 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>BullVeda · Watchlist</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr"/>
@@ -13440,12 +13440,12 @@
       </c>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>99cff7117</t>
         </is>
       </c>
       <c r="N233" s="8" t="inlineStr"/>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr"/>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr"/>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
@@ -13741,17 +13741,17 @@
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr"/>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N239" s="8" t="inlineStr"/>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
@@ -13795,17 +13795,17 @@
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr"/>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N240" s="8" t="inlineStr"/>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr"/>
@@ -13888,7 +13888,7 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr"/>
@@ -13996,7 +13996,7 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr"/>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
@@ -14129,7 +14129,7 @@
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr"/>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr"/>
@@ -14212,7 +14212,7 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr"/>
@@ -14266,7 +14266,7 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr"/>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr"/>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>CLEANUP-HOT-SECTORS</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
@@ -14384,22 +14384,22 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Code Hygiene / Signal Scanner</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>Remove dead panelHotSectors function</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr"/>
@@ -14412,23 +14412,23 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N251" s="8" t="inlineStr"/>
     </row>
-    <row r="252" ht="105" customHeight="1">
+    <row r="252" ht="45" customHeight="1">
       <c r="A252" s="2" t="n">
         <v>251</v>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>UI-CRYPTO-1</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
@@ -14438,22 +14438,22 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Crypto Tab</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>20yr HF analyst Crypto tab rebuild</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr"/>
@@ -14466,23 +14466,23 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N252" s="8" t="inlineStr"/>
     </row>
-    <row r="253" ht="75" customHeight="1">
+    <row r="253" ht="45" customHeight="1">
       <c r="A253" s="2" t="n">
         <v>252</v>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-T1CAT-1</t>
+          <t>CLEANUP-HOT-SECTORS</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
@@ -14492,22 +14492,22 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Code Hygiene / Signal Scanner</t>
         </is>
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>T1 CATALYST pill read wrong field</t>
+          <t>Remove dead panelHotSectors function</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
+          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
+          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr"/>
@@ -14520,23 +14520,23 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N253" s="8" t="inlineStr"/>
     </row>
-    <row r="254" ht="90" customHeight="1">
+    <row r="254" ht="105" customHeight="1">
       <c r="A254" s="2" t="n">
         <v>253</v>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>SCAN-AUDIT-LIVE-VS-BASE</t>
+          <t>UI-CRYPTO-1</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
@@ -14546,22 +14546,22 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Crypto Tab</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>Live realized edge vs baseline audit view</t>
+          <t>20yr HF analyst Crypto tab rebuild</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>Needed a signal audit: do live forward outcomes confirm the system's expected per-setup edge, or is it eroding/overfit?</t>
+          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>scripts/audit_live_vs_backtest.py joins audit_ledger resolved realized_r (live, OOS) to setup_stats haircut baseline per setup family; Wilson LB on live WR; CONFIRMED/SOFT/ERODING/THIN verdict (CONFIRMED=live&gt;=raw baseline); walk_forward backtest drops into cache/backtest_baseline.json as override; writes cache/audit_live_vs_backtest.json</t>
+          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr"/>
@@ -14574,23 +14574,23 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>d6f5f7112</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N254" s="8" t="inlineStr"/>
     </row>
-    <row r="255" ht="60" customHeight="1">
+    <row r="255" ht="75" customHeight="1">
       <c r="A255" s="2" t="n">
         <v>254</v>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>SCAN-SNAPSHOT-FULL-DETAIL</t>
+          <t>SCANNER-T1CAT-1</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
@@ -14600,22 +14600,22 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>Store full per-run scanner detail in DB with 3-month retention</t>
+          <t>T1 CATALYST pill read wrong field</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>ticker_snapshots stored only a 38-field whitelist in raw_json; full 292-field scanner payload was never archived (only latest in last_bundle.json). Full-every-run uncompressed=874GB/yr</t>
+          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>ticker_snapshots.py: store FULL payload gzipped in new raw_gz BLOB (~37MB/run, 53GB@90d), +5 flat cols (conviction_tier/target2/pct_chg/p_up/mode), purge_old() 90-day rolling retention + get_full() reader; ~589MB/day fits 162GB free disk</t>
+          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr"/>
@@ -14628,23 +14628,23 @@
       </c>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>8dee39a97</t>
+          <t>1d6fdb14a</t>
         </is>
       </c>
       <c r="N255" s="8" t="inlineStr"/>
     </row>
-    <row r="256" ht="60" customHeight="1">
+    <row r="256" ht="90" customHeight="1">
       <c r="A256" s="2" t="n">
         <v>255</v>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>SIGNAL-LEDGER-TIER-NULL</t>
+          <t>SCAN-AUDIT-LIVE-VS-BASE</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
@@ -14659,17 +14659,17 @@
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>tier/EQ/Cat logged null for swing rows in audit ledger</t>
+          <t>Live realized edge vs baseline audit view</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>build_audit_ledger signal_log ingestion dropped conviction_tier/entry_quality/catalyst_tier; field-name mismatch (signal_log uses conviction_label). 209 swing BUY rows had all 3 null</t>
+          <t>Needed a signal audit: do live forward outcomes confirm the system's expected per-setup edge, or is it eroding/overfit?</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>Map conviction_label-&gt;conviction_tier + entry_quality + catalyst_tier in signal_log record-creation AND augment paths (build_audit_ledger.py); verified 210/210 swing rows populated</t>
+          <t>scripts/audit_live_vs_backtest.py joins audit_ledger resolved realized_r (live, OOS) to setup_stats haircut baseline per setup family; Wilson LB on live WR; CONFIRMED/SOFT/ERODING/THIN verdict (CONFIRMED=live&gt;=raw baseline); walk_forward backtest drops into cache/backtest_baseline.json as override; writes cache/audit_live_vs_backtest.json</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr"/>
@@ -14687,18 +14687,18 @@
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>8dee39a97</t>
+          <t>d6f5f7112</t>
         </is>
       </c>
       <c r="N256" s="8" t="inlineStr"/>
     </row>
-    <row r="257" ht="75" customHeight="1">
+    <row r="257" ht="60" customHeight="1">
       <c r="A257" s="2" t="n">
         <v>256</v>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>EODHD-EDGAR-FUNDAMENTALS</t>
+          <t>SCAN-SNAPSHOT-FULL-DETAIL</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
@@ -14708,22 +14708,22 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future quality)</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
+          <t>Store full per-run scanner detail in DB with 3-month retention</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
+          <t>ticker_snapshots stored only a 38-field whitelist in raw_json; full 292-field scanner payload was never archived (only latest in last_bundle.json). Full-every-run uncompressed=874GB/yr</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>edgar_client.py + nightly batch</t>
+          <t>ticker_snapshots.py: store FULL payload gzipped in new raw_gz BLOB (~37MB/run, 53GB@90d), +5 flat cols (conviction_tier/target2/pct_chg/p_up/mode), purge_old() 90-day rolling retention + get_full() reader; ~589MB/day fits 162GB free disk</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr"/>
@@ -14736,23 +14736,23 @@
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>5d05268ef</t>
+          <t>8dee39a97</t>
         </is>
       </c>
       <c r="N257" s="8" t="inlineStr"/>
     </row>
-    <row r="258" ht="75" customHeight="1">
+    <row r="258" ht="60" customHeight="1">
       <c r="A258" s="2" t="n">
         <v>257</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-QUAL-REASON-1</t>
+          <t>SIGNAL-LEDGER-TIER-NULL</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Misleading entry_quality WATCH reason</t>
+          <t>tier/EQ/Cat logged null for swing rows in audit ledger</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
+          <t>build_audit_ledger signal_log ingestion dropped conviction_tier/entry_quality/catalyst_tier; field-name mismatch (signal_log uses conviction_label). 209 swing BUY rows had all 3 null</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
+          <t>Map conviction_label-&gt;conviction_tier + entry_quality + catalyst_tier in signal_log record-creation AND augment paths (build_audit_ledger.py); verified 210/210 swing rows populated</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr"/>
@@ -14790,23 +14790,23 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>613f10e35</t>
+          <t>8dee39a97</t>
         </is>
       </c>
       <c r="N258" s="8" t="inlineStr"/>
     </row>
-    <row r="259" ht="60" customHeight="1">
+    <row r="259" ht="75" customHeight="1">
       <c r="A259" s="2" t="n">
         <v>258</v>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>SETDETAIL-FALLBACK</t>
+          <t>EODHD-EDGAR-FUNDAMENTALS</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
@@ -14816,22 +14816,22 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Routing</t>
+          <t>Data / SEC EDGAR (future quality)</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>setDetailTicker failed for R2000-only tickers</t>
+          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
+          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>kairos.html window.setDetailTicker fallback block</t>
+          <t>edgar_client.py + nightly batch</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr"/>
@@ -14844,23 +14844,23 @@
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>5d05268ef</t>
         </is>
       </c>
       <c r="N259" s="8" t="inlineStr"/>
     </row>
-    <row r="260" ht="60" customHeight="1">
+    <row r="260" ht="75" customHeight="1">
       <c r="A260" s="2" t="n">
         <v>259</v>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>ENTRY-QUAL-REASON-1</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
@@ -14870,34 +14870,26 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Misleading entry_quality WATCH reason</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H260" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I260" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
+          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr"/>
+      <c r="I260" s="5" t="inlineStr"/>
       <c r="J260" s="5" t="inlineStr"/>
       <c r="K260" s="12" t="inlineStr">
         <is>
@@ -14906,27 +14898,23 @@
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N260" s="8" t="inlineStr">
-        <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="75" customHeight="1">
+          <t>613f10e35</t>
+        </is>
+      </c>
+      <c r="N260" s="8" t="inlineStr"/>
+    </row>
+    <row r="261" ht="45" customHeight="1">
       <c r="A261" s="2" t="n">
         <v>260</v>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>DESK-LOG-STALE-GUARD</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
@@ -14936,39 +14924,27 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Desks / Track Record</t>
         </is>
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Desk logger silent 0-append on stale bundle</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>log_today() froze the desk track-record when the 14:20 job hit a prior-session bundle</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
-        </is>
-      </c>
-      <c r="H261" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I261" s="5" t="inlineStr">
-        <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J261" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Guard on today PT date; skip stale bundle with a message so it captures once fresh bundle exists</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr"/>
+      <c r="I261" s="5" t="inlineStr"/>
+      <c r="J261" s="5" t="inlineStr"/>
       <c r="K261" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14976,27 +14952,23 @@
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N261" s="8" t="inlineStr">
-        <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="75" customHeight="1">
+          <t>9899c16f4</t>
+        </is>
+      </c>
+      <c r="N261" s="8" t="inlineStr"/>
+    </row>
+    <row r="262" ht="60" customHeight="1">
       <c r="A262" s="2" t="n">
         <v>261</v>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>SETDETAIL-FALLBACK</t>
         </is>
       </c>
       <c r="C262" s="10" t="inlineStr">
@@ -15006,22 +14978,22 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Detail UI / Routing</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>setDetailTicker failed for R2000-only tickers</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
+          <t>kairos.html window.setDetailTicker fallback block</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
@@ -15034,23 +15006,23 @@
       </c>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N262" s="8" t="inlineStr"/>
     </row>
-    <row r="263" ht="75" customHeight="1">
+    <row r="263" ht="60" customHeight="1">
       <c r="A263" s="2" t="n">
         <v>262</v>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>EXEC-PRICE-CAP-150</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C263" s="10" t="inlineStr">
@@ -15060,26 +15032,34 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Executor</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t>Executor-only $150 share-price cap (paper auto-buy)</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>Owner directive 2026-06-16: paper executor should trade only stocks &lt; $150 for share-granularity on the new $10k Alpaca paper account (PA38Z284EF12).</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>Added executor.max_entry_price=150 config knob + gate in build_order_plan after entry/stop/target validation. EXECUTOR-scoped only — filters.max_price stays $1000 so SIGNALS remain universal for all users. Tested: blocks $525 entry, passes $40. Set 0/null to disable.</t>
-        </is>
-      </c>
-      <c r="H263" s="2" t="inlineStr"/>
-      <c r="I263" s="5" t="inlineStr"/>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I263" s="5" t="inlineStr">
+        <is>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
       <c r="J263" s="5" t="inlineStr"/>
       <c r="K263" s="12" t="inlineStr">
         <is>
@@ -15088,23 +15068,27 @@
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>a61e2a906</t>
-        </is>
-      </c>
-      <c r="N263" s="8" t="inlineStr"/>
-    </row>
-    <row r="264" ht="60" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N263" s="8" t="inlineStr">
+        <is>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="75" customHeight="1">
       <c r="A264" s="2" t="n">
         <v>263</v>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>UI-HELP-1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
@@ -15114,27 +15098,39 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Help System</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Help registry expanded 14 to 38 entries</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
-        </is>
-      </c>
-      <c r="H264" s="2" t="inlineStr"/>
-      <c r="I264" s="5" t="inlineStr"/>
-      <c r="J264" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I264" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J264" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K264" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15142,23 +15138,27 @@
       </c>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
-        </is>
-      </c>
-      <c r="N264" s="8" t="inlineStr"/>
-    </row>
-    <row r="265" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N264" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="75" customHeight="1">
       <c r="A265" s="2" t="n">
         <v>264</v>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>HEAVY-JOB-STAGGER</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
@@ -15168,22 +15168,22 @@
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E265" s="6" t="inlineStr">
         <is>
-          <t>Stagger heavy morning jobs to stop load-starving the scan</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>Heavy jobs converged: edgar(95m) overlapped precompute at 3am (load 19); ml-predict(13 cores) collided with the 6-7am scan chain (load 36) -&gt; heavy_job_guard skipped scan/precompute/strategy-warm</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>edgar-fundamentals 02:00-&gt;01:00 (finishes before precompute 03:00); ml-predict morning run 06:45-&gt;08:00 (runs alone after scan chain). Load 36-&gt;4.4 after; timeline now sequential</t>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr"/>
@@ -15196,23 +15196,23 @@
       </c>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>84a85dcc9</t>
+          <t>8b06e56ae</t>
         </is>
       </c>
       <c r="N265" s="8" t="inlineStr"/>
     </row>
-    <row r="266" ht="45" customHeight="1">
+    <row r="266" ht="75" customHeight="1">
       <c r="A266" s="2" t="n">
         <v>265</v>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>EXEC-PRICE-CAP-150</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
@@ -15222,34 +15222,26 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Executor</t>
         </is>
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Executor-only $150 share-price cap (paper auto-buy)</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Owner directive 2026-06-16: paper executor should trade only stocks &lt; $150 for share-granularity on the new $10k Alpaca paper account (PA38Z284EF12).</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H266" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I266" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Added executor.max_entry_price=150 config knob + gate in build_order_plan after entry/stop/target validation. EXECUTOR-scoped only — filters.max_price stays $1000 so SIGNALS remain universal for all users. Tested: blocks $525 entry, passes $40. Set 0/null to disable.</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr"/>
+      <c r="I266" s="5" t="inlineStr"/>
       <c r="J266" s="5" t="inlineStr"/>
       <c r="K266" s="12" t="inlineStr">
         <is>
@@ -15258,19 +15250,15 @@
       </c>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N266" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
+          <t>a61e2a906</t>
+        </is>
+      </c>
+      <c r="N266" s="8" t="inlineStr"/>
     </row>
     <row r="267" ht="60" customHeight="1">
       <c r="A267" s="2" t="n">
@@ -15278,7 +15266,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>MAC-DISK-CLEANUP</t>
+          <t>UI-HELP-1</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
@@ -15288,22 +15276,22 @@
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Help System</t>
         </is>
       </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t>Reclaim local disk after NAS backup verified</t>
+          <t>Help registry expanded 14 to 38 entries</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>Disk 88% used; reclaim regenerable bulk safely now code+data verified on NAS</t>
+          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>Removed stale .git.bak (742M) + pruned cache/eodhd &gt;30d (1.36G, kept hot+state); cache/edgar all hot; big active caches left (refetch quota-expensive, 175G free ample)</t>
+          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr"/>
@@ -15316,23 +15304,23 @@
       </c>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>c2c4c85a0</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N267" s="8" t="inlineStr"/>
     </row>
-    <row r="268" ht="75" customHeight="1">
+    <row r="268" ht="60" customHeight="1">
       <c r="A268" s="2" t="n">
         <v>267</v>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>NAS-CODE-BACKUP</t>
+          <t>HEAVY-JOB-STAGGER</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
@@ -15347,17 +15335,17 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Code backup to NAS CodeBackup share</t>
+          <t>Stagger heavy morning jobs to stop load-starving the scan</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>Needed an off-Mac code backup before cleaning the 89%-full disk; rsync-over-SMB crawled on .git loose objects</t>
+          <t>Heavy jobs converged: edgar(95m) overlapped precompute at 3am (load 19); ml-predict(13 cores) collided with the 6-7am scan chain (load 36) -&gt; heavy_job_guard skipped scan/precompute/strategy-warm</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>scripts/backup_code_to_nas.sh: (A) git push --mirror to bare repo on NAS (efficient packed transfer, all branches), (B) rsync working files excl .git/cache/node_modules + SMB reserved names (CON/PRN/AUX/NUL). Verified via test-clone: 731 commits/4948 files. Nightly com.swingtrade.code-backup 21:00 PT</t>
+          <t>edgar-fundamentals 02:00-&gt;01:00 (finishes before precompute 03:00); ml-predict morning run 06:45-&gt;08:00 (runs alone after scan chain). Load 36-&gt;4.4 after; timeline now sequential</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr"/>
@@ -15370,23 +15358,23 @@
       </c>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>4c2deb164</t>
+          <t>84a85dcc9</t>
         </is>
       </c>
       <c r="N268" s="8" t="inlineStr"/>
     </row>
-    <row r="269" ht="75" customHeight="1">
+    <row r="269" ht="45" customHeight="1">
       <c r="A269" s="2" t="n">
         <v>268</v>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>NAS-HISTORY-SYNC</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
@@ -15401,21 +15389,29 @@
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>Sync all track-history to NAS deep store</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Only ticker_snapshots was on NAS; signal_log/audit_ledger/picks_history/ml_edge existed only locally — not a true backup</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>nas_pg.archive_json (JSONB archive, NaN-sanitized, in-batch dedup); scripts/sync_history_to_nas.py mirrors signal_log(4713)/audit_ledger(4915)/picks_trades(1766)/picks_runs(57)/ml_edge(1905); nightly via scripts/nas_sync_all.sh in com.swingtrade.nas-sync; 209,630 total rows on NAS</t>
-        </is>
-      </c>
-      <c r="H269" s="2" t="inlineStr"/>
-      <c r="I269" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I269" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J269" s="5" t="inlineStr"/>
       <c r="K269" s="12" t="inlineStr">
         <is>
@@ -15424,23 +15420,27 @@
       </c>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>cb4ef7114</t>
-        </is>
-      </c>
-      <c r="N269" s="8" t="inlineStr"/>
-    </row>
-    <row r="270" ht="90" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N269" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="60" customHeight="1">
       <c r="A270" s="2" t="n">
         <v>269</v>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>NAS-PG-DEEP-STORE</t>
+          <t>MAC-DISK-CLEANUP</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Self-hosted Postgres on Synology NAS as deep audit/snapshot store</t>
+          <t>Reclaim local disk after NAS backup verified</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Local SQLite limited by 162GB-free disk (89% full); full snapshot retention untenable locally. Owner has DS1520+ NAS</t>
+          <t>Disk 88% used; reclaim regenerable bulk safely now code+data verified on NAS</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Postgres 16 container on DS1520+ (192.168.1.25:5433); nas_pg.py (conn+schema+upsert), scripts/sync_snapshots_to_nas.py (idempotent push), ticker_snapshots.capture_scan best-effort real-time push, nightly catch-up launchd com.swingtrade.nas-sync. SQLite=hot 90d, NAS=full retention. 196K rows synced, raw_gz round-trips 292 fields. NAS_PG_URL in .env (gitignored)</t>
+          <t>Removed stale .git.bak (742M) + pruned cache/eodhd &gt;30d (1.36G, kept hot+state); cache/edgar all hot; big active caches left (refetch quota-expensive, 175G free ample)</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr"/>
@@ -15478,23 +15478,23 @@
       </c>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>76cca4dbd</t>
+          <t>c2c4c85a0</t>
         </is>
       </c>
       <c r="N270" s="8" t="inlineStr"/>
     </row>
-    <row r="271" ht="45" customHeight="1">
+    <row r="271" ht="75" customHeight="1">
       <c r="A271" s="2" t="n">
         <v>270</v>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>SCHWAB-EXPIRY-ALERT</t>
+          <t>NAS-CODE-BACKUP</t>
         </is>
       </c>
       <c r="C271" s="10" t="inlineStr">
@@ -15509,17 +15509,17 @@
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>Proactive Schwab refresh-token expiry warning</t>
+          <t>Code backup to NAS CodeBackup share</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>Schwab refresh token expired silently (7d hard expiry, daily job refreshes only the access token) -&gt; 4H/intraday/options/IV degraded mid-trading-day 2026-06-22</t>
+          <t>Needed an off-Mac code backup before cleaning the 89%-full disk; rsync-over-SMB crawled on .git loose objects</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>heartbeat_check.check_schwab_token() reads SCHWAB_REFRESH_ISSUED_AT, warns at 5d (2d runway before 7d expiry) via daily heartbeat Slack alert</t>
+          <t>scripts/backup_code_to_nas.sh: (A) git push --mirror to bare repo on NAS (efficient packed transfer, all branches), (B) rsync working files excl .git/cache/node_modules + SMB reserved names (CON/PRN/AUX/NUL). Verified via test-clone: 731 commits/4948 files. Nightly com.swingtrade.code-backup 21:00 PT</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr"/>
@@ -15532,12 +15532,12 @@
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>16a619c8f</t>
+          <t>4c2deb164</t>
         </is>
       </c>
       <c r="N271" s="8" t="inlineStr"/>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>SCHWAB-VALIDITY-ALERT</t>
+          <t>NAS-HISTORY-SYNC</t>
         </is>
       </c>
       <c r="C272" s="10" t="inlineStr">
@@ -15563,17 +15563,17 @@
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Schwab heartbeat alert was age-based, missed revoked tokens</t>
+          <t>Sync all track-history to NAS deep store</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29: Schwab refresh token was REJECTED (HTTP 400) while its local issue-age still read 0.5d 'fresh' — the age-based heartbeat check (SCHWAB-EXPIRY-ALERT) could not catch a revoked/invalid token, only an expired one. Schwab silently went dark twice (06-22, 06-29)</t>
+          <t>Only ticker_snapshots was on NAS; signal_log/audit_ledger/picks_history/ml_edge existed only locally — not a true backup</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>check_schwab_token.py touches .schwab_token_ok ONLY on a real probe success (removes on 400); heartbeat_check.check_schwab_token now alerts on missing/stale marker (validity) not age. Negative-tested</t>
+          <t>nas_pg.archive_json (JSONB archive, NaN-sanitized, in-batch dedup); scripts/sync_history_to_nas.py mirrors signal_log(4713)/audit_ledger(4915)/picks_trades(1766)/picks_runs(57)/ml_edge(1905); nightly via scripts/nas_sync_all.sh in com.swingtrade.nas-sync; 209,630 total rows on NAS</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr"/>
@@ -15586,23 +15586,23 @@
       </c>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>893daad5a</t>
+          <t>cb4ef7114</t>
         </is>
       </c>
       <c r="N272" s="8" t="inlineStr"/>
     </row>
-    <row r="273" ht="75" customHeight="1">
+    <row r="273" ht="90" customHeight="1">
       <c r="A273" s="2" t="n">
         <v>272</v>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>SYNC-FRESHNESS-WATCHDOG</t>
+          <t>NAS-PG-DEEP-STORE</t>
         </is>
       </c>
       <c r="C273" s="10" t="inlineStr">
@@ -15617,17 +15617,17 @@
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>Daily freshness alert if NAS data/code sync hasn't succeeded in 24h</t>
+          <t>Self-hosted Postgres on Synology NAS as deep audit/snapshot store</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>code-backup silently failed for days (exit=0 but 0s do-nothing on stale SMB mount); nothing alerted</t>
+          <t>Local SQLite limited by 162GB-free disk (89% full); full snapshot retention untenable locally. Owner has DS1520+ NAS</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>Both sync scripts write a success marker ONLY on genuine completion; heartbeat_check.py checks both markers &lt;26h (catches exit=0-but-0s); scheduled daily 08:00 via com.swingtrade.heartbeat (also fleet+close-loop). code-backup tightened to twice daily (09:00+21:00). Negative-tested: stale marker fires Slack alert</t>
+          <t>Postgres 16 container on DS1520+ (192.168.1.25:5433); nas_pg.py (conn+schema+upsert), scripts/sync_snapshots_to_nas.py (idempotent push), ticker_snapshots.capture_scan best-effort real-time push, nightly catch-up launchd com.swingtrade.nas-sync. SQLite=hot 90d, NAS=full retention. 196K rows synced, raw_gz round-trips 292 fields. NAS_PG_URL in .env (gitignored)</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr"/>
@@ -15640,23 +15640,23 @@
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>1e3869561</t>
+          <t>76cca4dbd</t>
         </is>
       </c>
       <c r="N273" s="8" t="inlineStr"/>
     </row>
-    <row r="274" ht="90" customHeight="1">
+    <row r="274" ht="45" customHeight="1">
       <c r="A274" s="2" t="n">
         <v>273</v>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>TUNNEL-HARDEN-247</t>
+          <t>SCHWAB-EXPIRY-ALERT</t>
         </is>
       </c>
       <c r="C274" s="10" t="inlineStr">
@@ -15671,17 +15671,17 @@
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Harden Mac+tunnel for 24/7 always-on serving</t>
+          <t>Proactive Schwab refresh-token expiry warning</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>Serving had two gaps: caffeinate only ran weekday 6:20a-1:20p (Mac could sleep nights/weekends -&gt; server+tunnel unreachable); healthcheck detected origin-down but only alerted a human (no self-heal, and KeepAlive cannot restart a HUNG server)</t>
+          <t>Schwab refresh token expired silently (7d hard expiry, daily job refreshes only the access token) -&gt; 4H/intraday/options/IV degraded mid-trading-day 2026-06-22</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>Added com.swingtrade.always-awake (caffeinate -i -s, KeepAlive, 24/7 wake lock); tunnel-healthcheck.sh now force-kickstarts com.swingtrade.server on 530/000/502/503/504 before alerting; alert reworded to fire only when self-heal FAILED. Server+cloudflared already had KeepAlive. Residual: cloudflared hang (1033) needs sudo to restart</t>
+          <t>heartbeat_check.check_schwab_token() reads SCHWAB_REFRESH_ISSUED_AT, warns at 5d (2d runway before 7d expiry) via daily heartbeat Slack alert</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr"/>
@@ -15694,23 +15694,23 @@
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>8b2395396</t>
+          <t>16a619c8f</t>
         </is>
       </c>
       <c r="N274" s="8" t="inlineStr"/>
     </row>
-    <row r="275" ht="90" customHeight="1">
+    <row r="275" ht="75" customHeight="1">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>UI-MLEDGE-1</t>
+          <t>SCHWAB-VALIDITY-ALERT</t>
         </is>
       </c>
       <c r="C275" s="10" t="inlineStr">
@@ -15720,22 +15720,22 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>ML Edge Tab</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>Theme switching + tf-* visual port</t>
+          <t>Schwab heartbeat alert was age-based, missed revoked tokens</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
+          <t>2026-06-29: Schwab refresh token was REJECTED (HTTP 400) while its local issue-age still read 0.5d 'fresh' — the age-based heartbeat check (SCHWAB-EXPIRY-ALERT) could not catch a revoked/invalid token, only an expired one. Schwab silently went dark twice (06-22, 06-29)</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+          <t>check_schwab_token.py touches .schwab_token_ok ONLY on a real probe success (removes on 400); heartbeat_check.check_schwab_token now alerts on missing/stale marker (validity) not age. Negative-tested</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr"/>
@@ -15748,23 +15748,23 @@
       </c>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>893daad5a</t>
         </is>
       </c>
       <c r="N275" s="8" t="inlineStr"/>
     </row>
-    <row r="276" ht="45" customHeight="1">
+    <row r="276" ht="75" customHeight="1">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>SYNC-FRESHNESS-WATCHDOG</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
@@ -15774,39 +15774,27 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Daily freshness alert if NAS data/code sync hasn't succeeded in 24h</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>code-backup silently failed for days (exit=0 but 0s do-nothing on stale SMB mount); nothing alerted</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
-        </is>
-      </c>
-      <c r="H276" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I276" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J276" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Both sync scripts write a success marker ONLY on genuine completion; heartbeat_check.py checks both markers &lt;26h (catches exit=0-but-0s); scheduled daily 08:00 via com.swingtrade.heartbeat (also fleet+close-loop). code-backup tightened to twice daily (09:00+21:00). Negative-tested: stale marker fires Slack alert</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr"/>
+      <c r="I276" s="5" t="inlineStr"/>
+      <c r="J276" s="5" t="inlineStr"/>
       <c r="K276" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15814,27 +15802,23 @@
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
-        </is>
-      </c>
-      <c r="N276" s="8" t="inlineStr">
-        <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="45" customHeight="1">
+          <t>1e3869561</t>
+        </is>
+      </c>
+      <c r="N276" s="8" t="inlineStr"/>
+    </row>
+    <row r="277" ht="90" customHeight="1">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>TUNNEL-HARDEN-247</t>
         </is>
       </c>
       <c r="C277" s="10" t="inlineStr">
@@ -15844,22 +15828,22 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>Harden Mac+tunnel for 24/7 always-on serving</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>Serving had two gaps: caffeinate only ran weekday 6:20a-1:20p (Mac could sleep nights/weekends -&gt; server+tunnel unreachable); healthcheck detected origin-down but only alerted a human (no self-heal, and KeepAlive cannot restart a HUNG server)</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
+          <t>Added com.swingtrade.always-awake (caffeinate -i -s, KeepAlive, 24/7 wake lock); tunnel-healthcheck.sh now force-kickstarts com.swingtrade.server on 530/000/502/503/504 before alerting; alert reworded to fire only when self-heal FAILED. Server+cloudflared already had KeepAlive. Residual: cloudflared hang (1033) needs sudo to restart</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr"/>
@@ -15872,23 +15856,23 @@
       </c>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
+          <t>8b2395396</t>
         </is>
       </c>
       <c r="N277" s="8" t="inlineStr"/>
     </row>
-    <row r="278" ht="45" customHeight="1">
+    <row r="278" ht="90" customHeight="1">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>FORENSICS-WEEKLY-SLACK</t>
+          <t>UI-MLEDGE-1</t>
         </is>
       </c>
       <c r="C278" s="10" t="inlineStr">
@@ -15898,22 +15882,22 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Notifications / Audit</t>
+          <t>ML Edge Tab</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>Weekly pick-forensics Slack digest</t>
+          <t>Theme switching + tf-* visual port</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
+          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr"/>
@@ -15926,23 +15910,23 @@
       </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N278" s="8" t="inlineStr"/>
     </row>
-    <row r="279" ht="75" customHeight="1">
+    <row r="279" ht="45" customHeight="1">
       <c r="A279" s="2" t="n">
         <v>278</v>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C279" s="10" t="inlineStr">
@@ -15952,37 +15936,37 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J279" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Sub-task of IPAD-1.</t>
         </is>
       </c>
       <c r="K279" s="12" t="inlineStr">
@@ -15992,27 +15976,27 @@
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>79fa01a75</t>
         </is>
       </c>
       <c r="N279" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="280" ht="60" customHeight="1">
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="45" customHeight="1">
       <c r="A280" s="2" t="n">
         <v>279</v>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C280" s="10" t="inlineStr">
@@ -16022,39 +16006,27 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
-        </is>
-      </c>
-      <c r="H280" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I280" s="5" t="inlineStr">
-        <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
-      <c r="J280" s="5" t="inlineStr">
-        <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
-        </is>
-      </c>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr"/>
+      <c r="I280" s="5" t="inlineStr"/>
+      <c r="J280" s="5" t="inlineStr"/>
       <c r="K280" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16062,27 +16034,23 @@
       </c>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N280" s="8" t="inlineStr">
-        <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="60" customHeight="1">
+          <t>d1ea97913</t>
+        </is>
+      </c>
+      <c r="N280" s="8" t="inlineStr"/>
+    </row>
+    <row r="281" ht="45" customHeight="1">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C281" s="10" t="inlineStr">
@@ -16092,39 +16060,27 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
-        </is>
-      </c>
-      <c r="H281" s="2" t="inlineStr">
-        <is>
-          <t>2-3 hrs</t>
-        </is>
-      </c>
-      <c r="I281" s="5" t="inlineStr">
-        <is>
-          <t>Win: safer registry edits + audit trail.</t>
-        </is>
-      </c>
-      <c r="J281" s="5" t="inlineStr">
-        <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr"/>
+      <c r="I281" s="5" t="inlineStr"/>
+      <c r="J281" s="5" t="inlineStr"/>
       <c r="K281" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16132,27 +16088,23 @@
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N281" s="8" t="inlineStr">
-        <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N281" s="8" t="inlineStr"/>
+    </row>
+    <row r="282" ht="75" customHeight="1">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C282" s="10" t="inlineStr">
@@ -16162,37 +16114,37 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I282" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J282" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K282" s="12" t="inlineStr">
@@ -16202,17 +16154,17 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N282" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16174,7 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C283" s="10" t="inlineStr">
@@ -16237,32 +16189,32 @@
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I283" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J283" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K283" s="12" t="inlineStr">
@@ -16272,27 +16224,27 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N283" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="284" ht="45" customHeight="1">
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="60" customHeight="1">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C284" s="10" t="inlineStr">
@@ -16302,27 +16254,39 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H284" s="2" t="inlineStr"/>
-      <c r="I284" s="5" t="inlineStr"/>
-      <c r="J284" s="5" t="inlineStr"/>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I284" s="5" t="inlineStr">
+        <is>
+          <t>Win: safer registry edits + audit trail.</t>
+        </is>
+      </c>
+      <c r="J284" s="5" t="inlineStr">
+        <is>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+        </is>
+      </c>
       <c r="K284" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16330,23 +16294,27 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N284" s="8" t="inlineStr"/>
-    </row>
-    <row r="285" ht="45" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N284" s="8" t="inlineStr">
+        <is>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="60" customHeight="1">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C285" s="10" t="inlineStr">
@@ -16356,27 +16324,39 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
-        </is>
-      </c>
-      <c r="H285" s="2" t="inlineStr"/>
-      <c r="I285" s="5" t="inlineStr"/>
-      <c r="J285" s="5" t="inlineStr"/>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I285" s="5" t="inlineStr">
+        <is>
+          <t>Win: visibility into RBAC changes.</t>
+        </is>
+      </c>
+      <c r="J285" s="5" t="inlineStr">
+        <is>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+        </is>
+      </c>
       <c r="K285" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16384,15 +16364,19 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N285" s="8" t="inlineStr"/>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N285" s="8" t="inlineStr">
+        <is>
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="60" customHeight="1">
       <c r="A286" s="2" t="n">
@@ -16400,7 +16384,7 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-TQ-LABEL</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C286" s="10" t="inlineStr">
@@ -16410,27 +16394,39 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
-        </is>
-      </c>
-      <c r="H286" s="2" t="inlineStr"/>
-      <c r="I286" s="5" t="inlineStr"/>
-      <c r="J286" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I286" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J286" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K286" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16438,23 +16434,27 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
-        </is>
-      </c>
-      <c r="N286" s="8" t="inlineStr"/>
-    </row>
-    <row r="287" ht="150" customHeight="1">
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N286" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="45" customHeight="1">
       <c r="A287" s="2" t="n">
         <v>286</v>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C287" s="10" t="inlineStr">
@@ -16464,31 +16464,27 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr"/>
       <c r="I287" s="5" t="inlineStr"/>
-      <c r="J287" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J287" s="5" t="inlineStr"/>
       <c r="K287" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16496,27 +16492,23 @@
       </c>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N287" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="105" customHeight="1">
+          <t>0dc7675ee</t>
+        </is>
+      </c>
+      <c r="N287" s="8" t="inlineStr"/>
+    </row>
+    <row r="288" ht="45" customHeight="1">
       <c r="A288" s="2" t="n">
         <v>287</v>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>SMC-OB-DISPLAY-1</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C288" s="10" t="inlineStr">
@@ -16526,22 +16518,22 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>OB confluence badges in SMC tab</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr"/>
@@ -16554,23 +16546,23 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>8182c3977</t>
+          <t>0dc7675ee</t>
         </is>
       </c>
       <c r="N288" s="8" t="inlineStr"/>
     </row>
-    <row r="289" ht="75" customHeight="1">
+    <row r="289" ht="60" customHeight="1">
       <c r="A289" s="2" t="n">
         <v>288</v>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-COMPANY-NAMES</t>
+          <t>OVERVIEW-TQ-LABEL</t>
         </is>
       </c>
       <c r="C289" s="10" t="inlineStr">
@@ -16580,22 +16572,22 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Scanner UI</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>NAME column duplicated TICKER (no company names)</t>
+          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>Scan feed set name=ticker; no cached name source (fundamentals.db raw_json has 0 names). NAME column was redundant.</t>
+          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>Free Wikipedia S&amp;P1500+NDX+Dow name map (scripts/build_ticker_names.py -&gt; cache/ticker_names.json, 1508 names); joined in /api/universe _ticker_names(); weekly refresh in weekly_diagnostics.sh. 70% live coverage, honest ticker fallback for the tail. No paid data.</t>
+          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr"/>
@@ -16608,23 +16600,23 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
-          <t>48f6a2fbf</t>
+          <t>15f8f9600</t>
         </is>
       </c>
       <c r="N289" s="8" t="inlineStr"/>
     </row>
-    <row r="290" ht="90" customHeight="1">
+    <row r="290" ht="150" customHeight="1">
       <c r="A290" s="2" t="n">
         <v>289</v>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>MR-KNIFE-GUARD</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C290" s="10" t="inlineStr">
@@ -16634,27 +16626,31 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Screener Desks</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>MR desk falling-knife guard</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>Mean-Reversion desk BUY (RSI&lt;30 &amp; &gt;200EMA) surfaced VIST — a deep-knife (rs 0) breakdown — as a BUY. No guard distinguishing oversold dip from oversold-breakdown.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>Flag-gated config.screener_desks.mr_falling_knife_guard: demote BUY-&gt;WATCH when rs_rank&lt;rs_min (deep knife). Signal-replay (scripts/backtest_mr_guard.py, 673 events) refuted the bear-stack/rs30 first guess, recalibrated to rs&lt;15 (KEEP WR 57% vs REJECT +0.06%). Display-only, gates no canonical verdict. PROVISIONAL: n=76 KEEP, one regime, in-sample.</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr"/>
       <c r="I290" s="5" t="inlineStr"/>
-      <c r="J290" s="5" t="inlineStr"/>
+      <c r="J290" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K290" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16662,23 +16658,27 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
-          <t>962b0baa2</t>
-        </is>
-      </c>
-      <c r="N290" s="8" t="inlineStr"/>
-    </row>
-    <row r="291" ht="45" customHeight="1">
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N290" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="105" customHeight="1">
       <c r="A291" s="2" t="n">
         <v>290</v>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>SMC-OB-DISPLAY-1</t>
         </is>
       </c>
       <c r="C291" s="10" t="inlineStr">
@@ -16688,22 +16688,22 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>OB confluence badges in SMC tab</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr"/>
@@ -16716,23 +16716,23 @@
       </c>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>8182c3977</t>
         </is>
       </c>
       <c r="N291" s="8" t="inlineStr"/>
     </row>
-    <row r="292" ht="45" customHeight="1">
+    <row r="292" ht="75" customHeight="1">
       <c r="A292" s="2" t="n">
         <v>291</v>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SCANNER-COMPANY-NAMES</t>
         </is>
       </c>
       <c r="C292" s="10" t="inlineStr">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Scanner UI</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>NAME column duplicated TICKER (no company names)</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Scan feed set name=ticker; no cached name source (fundamentals.db raw_json has 0 names). NAME column was redundant.</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Free Wikipedia S&amp;P1500+NDX+Dow name map (scripts/build_ticker_names.py -&gt; cache/ticker_names.json, 1508 names); joined in /api/universe _ticker_names(); weekly refresh in weekly_diagnostics.sh. 70% live coverage, honest ticker fallback for the tail. No paid data.</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr"/>
@@ -16770,23 +16770,23 @@
       </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>48f6a2fbf</t>
         </is>
       </c>
       <c r="N292" s="8" t="inlineStr"/>
     </row>
-    <row r="293" ht="45" customHeight="1">
+    <row r="293" ht="90" customHeight="1">
       <c r="A293" s="2" t="n">
         <v>292</v>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>MR-KNIFE-GUARD</t>
         </is>
       </c>
       <c r="C293" s="10" t="inlineStr">
@@ -16796,22 +16796,22 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Screener Desks</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>MR desk falling-knife guard</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Mean-Reversion desk BUY (RSI&lt;30 &amp; &gt;200EMA) surfaced VIST — a deep-knife (rs 0) breakdown — as a BUY. No guard distinguishing oversold dip from oversold-breakdown.</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>Flag-gated config.screener_desks.mr_falling_knife_guard: demote BUY-&gt;WATCH when rs_rank&lt;rs_min (deep knife). Signal-replay (scripts/backtest_mr_guard.py, 673 events) refuted the bear-stack/rs30 first guess, recalibrated to rs&lt;15 (KEEP WR 57% vs REJECT +0.06%). Display-only, gates no canonical verdict. PROVISIONAL: n=76 KEEP, one regime, in-sample.</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr"/>
@@ -16824,12 +16824,12 @@
       </c>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>962b0baa2</t>
         </is>
       </c>
       <c r="N293" s="8" t="inlineStr"/>
@@ -16840,7 +16840,7 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C294" s="10" t="inlineStr">
@@ -16855,17 +16855,17 @@
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr"/>
@@ -16894,7 +16894,7 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C295" s="10" t="inlineStr">
@@ -16909,17 +16909,17 @@
       </c>
       <c r="E295" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr"/>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C296" s="10" t="inlineStr">
@@ -16963,17 +16963,17 @@
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr"/>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C297" s="10" t="inlineStr">
@@ -17017,17 +17017,17 @@
       </c>
       <c r="E297" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr"/>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C298" s="10" t="inlineStr">
@@ -17071,17 +17071,17 @@
       </c>
       <c r="E298" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr"/>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C299" s="10" t="inlineStr">
@@ -17125,17 +17125,17 @@
       </c>
       <c r="E299" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F299" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr"/>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C300" s="10" t="inlineStr">
@@ -17179,17 +17179,17 @@
       </c>
       <c r="E300" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr"/>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C301" s="10" t="inlineStr">
@@ -17233,17 +17233,17 @@
       </c>
       <c r="E301" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr"/>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C302" s="10" t="inlineStr">
@@ -17287,17 +17287,17 @@
       </c>
       <c r="E302" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F302" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr"/>
@@ -17320,13 +17320,13 @@
       </c>
       <c r="N302" s="8" t="inlineStr"/>
     </row>
-    <row r="303" ht="60" customHeight="1">
+    <row r="303" ht="45" customHeight="1">
       <c r="A303" s="2" t="n">
         <v>302</v>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-RECUR-CHIP</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C303" s="10" t="inlineStr">
@@ -17336,22 +17336,22 @@
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>Signal Scanner</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E303" s="6" t="inlineStr">
         <is>
-          <t>Recurrence chip</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr"/>
@@ -17364,23 +17364,23 @@
       </c>
       <c r="L303" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
-          <t>cf702f2b4</t>
+          <t>dbbd6b5f6</t>
         </is>
       </c>
       <c r="N303" s="8" t="inlineStr"/>
     </row>
-    <row r="304" ht="120" customHeight="1">
+    <row r="304" ht="45" customHeight="1">
       <c r="A304" s="2" t="n">
         <v>303</v>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C304" s="10" t="inlineStr">
@@ -17390,39 +17390,27 @@
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E304" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H304" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I304" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J304" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr"/>
+      <c r="I304" s="5" t="inlineStr"/>
+      <c r="J304" s="5" t="inlineStr"/>
       <c r="K304" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -17430,27 +17418,23 @@
       </c>
       <c r="L304" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M304" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N304" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="305" ht="75" customHeight="1">
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N304" s="8" t="inlineStr"/>
+    </row>
+    <row r="305" ht="45" customHeight="1">
       <c r="A305" s="2" t="n">
         <v>304</v>
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C305" s="10" t="inlineStr">
@@ -17460,22 +17444,22 @@
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E305" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr"/>
@@ -17493,7 +17477,7 @@
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
+          <t>dbbd6b5f6</t>
         </is>
       </c>
       <c r="N305" s="8" t="inlineStr"/>
@@ -17504,7 +17488,7 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-1</t>
+          <t>SCANNER-RECUR-CHIP</t>
         </is>
       </c>
       <c r="C306" s="10" t="inlineStr">
@@ -17514,22 +17498,22 @@
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Signal Scanner</t>
         </is>
       </c>
       <c r="E306" s="6" t="inlineStr">
         <is>
-          <t>Signal -&gt; options-structure mapper</t>
+          <t>Recurrence chip</t>
         </is>
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
-          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
+          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
+          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr"/>
@@ -17542,23 +17526,23 @@
       </c>
       <c r="L306" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>cf702f2b4</t>
         </is>
       </c>
       <c r="N306" s="8" t="inlineStr"/>
     </row>
-    <row r="307" ht="45" customHeight="1">
+    <row r="307" ht="120" customHeight="1">
       <c r="A307" s="2" t="n">
         <v>306</v>
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-2</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C307" s="10" t="inlineStr">
@@ -17568,27 +17552,39 @@
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E307" s="6" t="inlineStr">
         <is>
-          <t>Contract selection from Schwab chain</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F307" s="5" t="inlineStr">
         <is>
-          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
-        </is>
-      </c>
-      <c r="H307" s="2" t="inlineStr"/>
-      <c r="I307" s="5" t="inlineStr"/>
-      <c r="J307" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I307" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J307" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K307" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -17596,23 +17592,27 @@
       </c>
       <c r="L307" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
-        </is>
-      </c>
-      <c r="N307" s="8" t="inlineStr"/>
-    </row>
-    <row r="308" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N307" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="75" customHeight="1">
       <c r="A308" s="2" t="n">
         <v>307</v>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-3</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C308" s="10" t="inlineStr">
@@ -17622,22 +17622,22 @@
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
         <is>
-          <t>Alpaca paper options orders in executor.py</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F308" s="5" t="inlineStr">
         <is>
-          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr"/>
@@ -17650,23 +17650,23 @@
       </c>
       <c r="L308" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M308" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N308" s="8" t="inlineStr"/>
     </row>
-    <row r="309" ht="45" customHeight="1">
+    <row r="309" ht="60" customHeight="1">
       <c r="A309" s="2" t="n">
         <v>308</v>
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-4</t>
+          <t>OPT-PAPER-1</t>
         </is>
       </c>
       <c r="C309" s="10" t="inlineStr">
@@ -17681,17 +17681,17 @@
       </c>
       <c r="E309" s="6" t="inlineStr">
         <is>
-          <t>Options position tracking + contract P&amp;L</t>
+          <t>Signal -&gt; options-structure mapper</t>
         </is>
       </c>
       <c r="F309" s="5" t="inlineStr">
         <is>
-          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
+          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
+          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr"/>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="M309" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N309" s="8" t="inlineStr"/>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-5</t>
+          <t>OPT-PAPER-2</t>
         </is>
       </c>
       <c r="C310" s="10" t="inlineStr">
@@ -17735,17 +17735,17 @@
       </c>
       <c r="E310" s="6" t="inlineStr">
         <is>
-          <t>Options-specific exits</t>
+          <t>Contract selection from Schwab chain</t>
         </is>
       </c>
       <c r="F310" s="5" t="inlineStr">
         <is>
-          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
+          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
+          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr"/>
@@ -17763,18 +17763,18 @@
       </c>
       <c r="M310" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N310" s="8" t="inlineStr"/>
     </row>
-    <row r="311" ht="120" customHeight="1">
+    <row r="311" ht="60" customHeight="1">
       <c r="A311" s="2" t="n">
         <v>310</v>
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>OPT-PAPER-3</t>
         </is>
       </c>
       <c r="C311" s="10" t="inlineStr">
@@ -17784,22 +17784,22 @@
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E311" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Alpaca paper options orders in executor.py</t>
         </is>
       </c>
       <c r="F311" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr"/>
@@ -17812,23 +17812,23 @@
       </c>
       <c r="L311" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M311" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N311" s="8" t="inlineStr"/>
     </row>
-    <row r="312" ht="60" customHeight="1">
+    <row r="312" ht="45" customHeight="1">
       <c r="A312" s="2" t="n">
         <v>311</v>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>TE-SESSION-CACHE</t>
+          <t>OPT-PAPER-4</t>
         </is>
       </c>
       <c r="C312" s="10" t="inlineStr">
@@ -17838,22 +17838,22 @@
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Structural Targets</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E312" s="6" t="inlineStr">
         <is>
-          <t>Session-date cache invalidation</t>
+          <t>Options position tracking + contract P&amp;L</t>
         </is>
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
-          <t>target_engine cache used 12h wall-clock TTL → expired mid-session (15:00-19:30 PT dead-zone) causing on-demand recomputes on tab open</t>
+          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>Switched _cache_is_fresh to session-date keying (_latest_completed_session) + 36h backstop + legacy grandfather; _cache_write stamps session_date. 0 added EODHD, recompute only on new daily bar.</t>
+          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr"/>
@@ -17866,23 +17866,23 @@
       </c>
       <c r="L312" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
-          <t>33146be5e</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N312" s="8" t="inlineStr"/>
     </row>
-    <row r="313" ht="60" customHeight="1">
+    <row r="313" ht="45" customHeight="1">
       <c r="A313" s="2" t="n">
         <v>312</v>
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>TE-STRATEGY-MODE</t>
+          <t>OPT-PAPER-5</t>
         </is>
       </c>
       <c r="C313" s="10" t="inlineStr">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>Target Engine</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E313" s="6" t="inlineStr">
         <is>
-          <t>_strategy_mode read but never written</t>
+          <t>Options-specific exits</t>
         </is>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
+          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
+          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr"/>
@@ -17920,23 +17920,23 @@
       </c>
       <c r="L313" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M313" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N313" s="8" t="inlineStr"/>
     </row>
-    <row r="314" ht="105" customHeight="1">
+    <row r="314" ht="120" customHeight="1">
       <c r="A314" s="2" t="n">
         <v>313</v>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C314" s="10" t="inlineStr">
@@ -17946,31 +17946,27 @@
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F314" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr"/>
       <c r="I314" s="5" t="inlineStr"/>
-      <c r="J314" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J314" s="5" t="inlineStr"/>
       <c r="K314" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -17978,27 +17974,23 @@
       </c>
       <c r="L314" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M314" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N314" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="135" customHeight="1">
+          <t>93ec11842</t>
+        </is>
+      </c>
+      <c r="N314" s="8" t="inlineStr"/>
+    </row>
+    <row r="315" ht="60" customHeight="1">
       <c r="A315" s="2" t="n">
         <v>314</v>
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TE-SESSION-CACHE</t>
         </is>
       </c>
       <c r="C315" s="10" t="inlineStr">
@@ -18008,39 +18000,27 @@
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Structural Targets</t>
         </is>
       </c>
       <c r="E315" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Session-date cache invalidation</t>
         </is>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>target_engine cache used 12h wall-clock TTL → expired mid-session (15:00-19:30 PT dead-zone) causing on-demand recomputes on tab open</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H315" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I315" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
-      <c r="J315" s="5" t="inlineStr">
-        <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
-        </is>
-      </c>
+          <t>Switched _cache_is_fresh to session-date keying (_latest_completed_session) + 36h backstop + legacy grandfather; _cache_write stamps session_date. 0 added EODHD, recompute only on new daily bar.</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr"/>
+      <c r="I315" s="5" t="inlineStr"/>
+      <c r="J315" s="5" t="inlineStr"/>
       <c r="K315" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -18048,27 +18028,23 @@
       </c>
       <c r="L315" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M315" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
-        </is>
-      </c>
-      <c r="N315" s="8" t="inlineStr">
-        <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="316" ht="45" customHeight="1">
+          <t>33146be5e</t>
+        </is>
+      </c>
+      <c r="N315" s="8" t="inlineStr"/>
+    </row>
+    <row r="316" ht="60" customHeight="1">
       <c r="A316" s="2" t="n">
         <v>315</v>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>TE-STRATEGY-MODE</t>
         </is>
       </c>
       <c r="C316" s="10" t="inlineStr">
@@ -18078,22 +18054,22 @@
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>Target Engine</t>
         </is>
       </c>
       <c r="E316" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>_strategy_mode read but never written</t>
         </is>
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
+          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr"/>
@@ -18106,23 +18082,23 @@
       </c>
       <c r="L316" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M316" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
+          <t>15f8f9600</t>
         </is>
       </c>
       <c r="N316" s="8" t="inlineStr"/>
     </row>
-    <row r="317" ht="120" customHeight="1">
+    <row r="317" ht="105" customHeight="1">
       <c r="A317" s="2" t="n">
         <v>316</v>
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C317" s="10" t="inlineStr">
@@ -18132,29 +18108,29 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E317" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F317" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr"/>
       <c r="I317" s="5" t="inlineStr"/>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K317" s="12" t="inlineStr">
@@ -18174,17 +18150,17 @@
       </c>
       <c r="N317" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="318" ht="60" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="135" customHeight="1">
       <c r="A318" s="2" t="n">
         <v>317</v>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C318" s="10" t="inlineStr">
@@ -18194,27 +18170,39 @@
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E318" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
-        </is>
-      </c>
-      <c r="H318" s="2" t="inlineStr"/>
-      <c r="I318" s="5" t="inlineStr"/>
-      <c r="J318" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I318" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J318" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K318" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -18222,23 +18210,27 @@
       </c>
       <c r="L318" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M318" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N318" s="8" t="inlineStr"/>
-    </row>
-    <row r="319" ht="60" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N318" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="45" customHeight="1">
       <c r="A319" s="2" t="n">
         <v>318</v>
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C319" s="10" t="inlineStr">
@@ -18248,22 +18240,22 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E319" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr"/>
@@ -18276,63 +18268,55 @@
       </c>
       <c r="L319" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>50cace567</t>
         </is>
       </c>
       <c r="N319" s="8" t="inlineStr"/>
     </row>
-    <row r="320" ht="45" customHeight="1">
+    <row r="320" ht="120" customHeight="1">
       <c r="A320" s="2" t="n">
         <v>319</v>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C320" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>RECENCY-FLOOR</t>
+        </is>
+      </c>
+      <c r="C320" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E320" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F320" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H320" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I320" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr"/>
+      <c r="I320" s="5" t="inlineStr"/>
       <c r="J320" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
         </is>
       </c>
       <c r="K320" s="12" t="inlineStr">
@@ -18342,65 +18326,57 @@
       </c>
       <c r="L320" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M320" s="3" t="inlineStr"/>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M320" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="N320" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
-    </row>
-    <row r="321" ht="45" customHeight="1">
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="60" customHeight="1">
       <c r="A321" s="2" t="n">
         <v>320</v>
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C321" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>MOMENTUM-TAB</t>
+        </is>
+      </c>
+      <c r="C321" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E321" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
-        </is>
-      </c>
-      <c r="H321" s="2" t="inlineStr">
-        <is>
-          <t>verified (no change needed)</t>
-        </is>
-      </c>
-      <c r="I321" s="5" t="inlineStr">
-        <is>
-          <t>Win: confirms infrastructure still healthy.</t>
-        </is>
-      </c>
-      <c r="J321" s="5" t="inlineStr">
-        <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr"/>
+      <c r="I321" s="5" t="inlineStr"/>
+      <c r="J321" s="5" t="inlineStr"/>
       <c r="K321" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -18408,60 +18384,52 @@
       </c>
       <c r="L321" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M321" s="3" t="inlineStr"/>
-      <c r="N321" s="8" t="inlineStr">
-        <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
-        </is>
-      </c>
-    </row>
-    <row r="322" ht="45" customHeight="1">
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M321" s="3" t="inlineStr">
+        <is>
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N321" s="8" t="inlineStr"/>
+    </row>
+    <row r="322" ht="60" customHeight="1">
       <c r="A322" s="2" t="n">
         <v>321</v>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
-        </is>
-      </c>
-      <c r="C322" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C322" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E322" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
-        </is>
-      </c>
-      <c r="H322" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I322" s="5" t="inlineStr">
-        <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr"/>
+      <c r="I322" s="5" t="inlineStr"/>
       <c r="J322" s="5" t="inlineStr"/>
       <c r="K322" s="12" t="inlineStr">
         <is>
@@ -18470,19 +18438,15 @@
       </c>
       <c r="L322" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
-      <c r="N322" s="8" t="inlineStr">
-        <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
-        </is>
-      </c>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N322" s="8" t="inlineStr"/>
     </row>
     <row r="323" ht="45" customHeight="1">
       <c r="A323" s="2" t="n">
@@ -18490,59 +18454,63 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C323" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C323" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E323" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F323" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I323" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J323" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K323" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L323" s="2" t="inlineStr"/>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
+      <c r="K323" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M323" s="3" t="inlineStr"/>
       <c r="N323" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -18552,59 +18520,63 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
-        </is>
-      </c>
-      <c r="C324" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C324" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E324" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F324" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I324" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: confirms infrastructure still healthy.</t>
         </is>
       </c>
       <c r="J324" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
-        </is>
-      </c>
-      <c r="K324" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L324" s="2" t="inlineStr"/>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K324" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L324" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M324" s="3" t="inlineStr"/>
       <c r="N324" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -18614,257 +18586,447 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C325" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C325" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E325" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F325" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I325" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J325" s="5" t="inlineStr">
-        <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K325" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L325" s="2" t="inlineStr"/>
-      <c r="M325" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J325" s="5" t="inlineStr"/>
+      <c r="K325" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L325" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M325" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N325" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="326" ht="75" customHeight="1">
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="45" customHeight="1">
       <c r="A326" s="2" t="n">
         <v>325</v>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C326" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C326" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E326" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F326" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I326" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J326" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
-        </is>
-      </c>
-      <c r="K326" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L326" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K326" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L326" s="2" t="inlineStr"/>
       <c r="M326" s="3" t="inlineStr"/>
       <c r="N326" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="327" ht="195" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="45" customHeight="1">
       <c r="A327" s="2" t="n">
         <v>326</v>
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C327" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D327" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E327" s="6" t="inlineStr">
+        <is>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+        </is>
+      </c>
+      <c r="F327" s="5" t="inlineStr">
+        <is>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+        </is>
+      </c>
+      <c r="G327" s="5" t="inlineStr">
+        <is>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>hours-days each</t>
+        </is>
+      </c>
+      <c r="I327" s="5" t="inlineStr">
+        <is>
+          <t>Win varies; defer until PERF-7 measured.</t>
+        </is>
+      </c>
+      <c r="J327" s="5" t="inlineStr">
+        <is>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K327" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L327" s="2" t="inlineStr"/>
+      <c r="M327" s="3" t="inlineStr"/>
+      <c r="N327" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="45" customHeight="1">
+      <c r="A328" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D328" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E328" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F328" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G328" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I328" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J328" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K328" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L328" s="2" t="inlineStr"/>
+      <c r="M328" s="3" t="inlineStr"/>
+      <c r="N328" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="75" customHeight="1">
+      <c r="A329" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C329" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D329" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E329" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F329" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G329" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I329" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J329" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K329" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M329" s="3" t="inlineStr"/>
+      <c r="N329" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="195" customHeight="1">
+      <c r="A330" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C327" s="10" t="inlineStr">
+      <c r="C330" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D327" s="5" t="inlineStr">
+      <c r="D330" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="E330" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F327" s="5" t="inlineStr">
+      <c r="F330" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G327" s="5" t="inlineStr">
+      <c r="G330" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H327" s="2" t="inlineStr">
+      <c r="H330" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I327" s="5" t="inlineStr">
+      <c r="I330" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J327" s="5" t="inlineStr">
+      <c r="J330" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K327" s="15" t="inlineStr">
+      <c r="K330" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L327" s="2" t="inlineStr">
+      <c r="L330" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="M327" s="3" t="inlineStr"/>
-      <c r="N327" s="8" t="inlineStr">
+      <c r="M330" s="3" t="inlineStr"/>
+      <c r="N330" s="8" t="inlineStr">
         <is>
           <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
         </is>
       </c>
     </row>
-    <row r="328" ht="90" customHeight="1">
-      <c r="A328" s="2" t="n">
-        <v>327</v>
-      </c>
-      <c r="B328" s="3" t="inlineStr">
+    <row r="331" ht="90" customHeight="1">
+      <c r="A331" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C328" s="13" t="inlineStr">
+      <c r="C331" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D328" s="5" t="inlineStr">
+      <c r="D331" s="5" t="inlineStr">
         <is>
           <t>Data / Universe</t>
         </is>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="E331" s="6" t="inlineStr">
         <is>
           <t>Russell 1000 historical membership (Sharadar SF1)</t>
         </is>
       </c>
-      <c r="F328" s="5" t="inlineStr">
+      <c r="F331" s="5" t="inlineStr">
         <is>
           <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
         </is>
       </c>
-      <c r="G328" s="5" t="inlineStr">
+      <c r="G331" s="5" t="inlineStr">
         <is>
           <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
         </is>
       </c>
-      <c r="H328" s="2" t="inlineStr">
+      <c r="H331" s="2" t="inlineStr">
         <is>
           <t>$$ + 1 day</t>
         </is>
       </c>
-      <c r="I328" s="5" t="inlineStr">
+      <c r="I331" s="5" t="inlineStr">
         <is>
           <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
         </is>
       </c>
-      <c r="J328" s="5" t="inlineStr">
+      <c r="J331" s="5" t="inlineStr">
         <is>
           <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
         </is>
       </c>
-      <c r="K328" s="15" t="inlineStr">
+      <c r="K331" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L328" s="2" t="inlineStr">
+      <c r="L331" s="2" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="M328" s="3" t="inlineStr"/>
-      <c r="N328" s="8" t="inlineStr">
+      <c r="M331" s="3" t="inlineStr"/>
+      <c r="N331" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -18966,13 +19128,13 @@
         <v>34</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
@@ -19023,13 +19185,13 @@
         <v>37</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
